--- a/product_surveys/020_skincare_fragrance_free_preference_survey--product_surveys.xlsx
+++ b/product_surveys/020_skincare_fragrance_free_preference_survey--product_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -918,8 +918,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -947,12 +947,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'skincare'}</t>
+          <t>skincare</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Skincare'}</t>
+          <t>Skincare</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'fragrance'}</t>
+          <t>fragrance</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Fragrance'}</t>
+          <t>Fragrance</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'haircare'}</t>
+          <t>haircare</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Haircare'}</t>
+          <t>Haircare</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'makeup'}</t>
+          <t>makeup</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Makeup'}</t>
+          <t>Makeup</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'bodycare'}</t>
+          <t>bodycare</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Bodycare'}</t>
+          <t>Bodycare</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Normal'}</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'sensitive'}</t>
+          <t>sensitive</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Sensitive'}</t>
+          <t>Sensitive</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'oily'}</t>
+          <t>oily</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Oily'}</t>
+          <t>Oily</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'dry'}</t>
+          <t>dry</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Dry'}</t>
+          <t>Dry</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'combination'}</t>
+          <t>combination</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Combination'}</t>
+          <t>Combination</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Not sure'}</t>
+          <t>Not sure</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Not sure'}</t>
+          <t>Not sure</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'fragrance_free'}</t>
+          <t>fragrance_free</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Fragrance free'}</t>
+          <t>Fragrance free</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'fragrance'}</t>
+          <t>fragrance</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Fragrance'}</t>
+          <t>Fragrance</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Not sure'}</t>
+          <t>Not sure</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Not sure'}</t>
+          <t>Not sure</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'fragrance'}</t>
+          <t>fragrance</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Fragrance'}</t>
+          <t>Fragrance</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'dye'}</t>
+          <t>dye</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Dye'}</t>
+          <t>Dye</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'sulfite'}</t>
+          <t>sulfite</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Sulfite'}</t>
+          <t>Sulfite</t>
         </is>
       </c>
     </row>
